--- a/basedatos_partidas/salida/descompuestos/CT-04-01-070.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-04-01-070.xlsx
@@ -539,10 +539,10 @@
         <v>0.13</v>
       </c>
       <c r="G10" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H10" t="n">
-        <v>14.95</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>14.85</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="12">
@@ -617,10 +617,10 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>13.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>54.66</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="18">
@@ -932,10 +932,10 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>72.36</v>
+        <v>65</v>
       </c>
       <c r="H29" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="30">
@@ -951,7 +951,7 @@
       </c>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="5" t="n">
-        <v>73.08</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-04-01-070.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-04-01-070.xlsx
@@ -591,10 +591,10 @@
         <v>1.8</v>
       </c>
       <c r="G12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H12" t="n">
-        <v>10.08</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -643,10 +643,10 @@
         <v>0.35</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.63</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="15">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.3</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="18">
@@ -932,7 +932,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>65</v>
+        <v>64.92</v>
       </c>
       <c r="H29" t="n">
         <v>0.65</v>
@@ -951,7 +951,7 @@
       </c>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="5" t="n">
-        <v>65.65000000000001</v>
+        <v>65.56999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-04-01-070.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-04-01-070.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 04 Fundaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Bases y zapatas</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
